--- a/panele-sterowania/Panel-C.xlsx
+++ b/panele-sterowania/Panel-C.xlsx
@@ -17145,7 +17145,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         </is>
       </c>
       <c r="D206" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         </is>
       </c>
       <c r="D207" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         </is>
       </c>
       <c r="D224" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         </is>
       </c>
       <c r="D233" s="2" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="D243" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         </is>
       </c>
       <c r="D251" s="2" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         </is>
       </c>
       <c r="D252" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         </is>
       </c>
       <c r="D260" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="D269" s="2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         </is>
       </c>
       <c r="D270" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         </is>
       </c>
       <c r="D278" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         </is>
       </c>
       <c r="D279" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         </is>
       </c>
       <c r="D287" s="2" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         </is>
       </c>
       <c r="D296" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         </is>
       </c>
       <c r="D305" s="2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="D314" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         </is>
       </c>
       <c r="D323" s="2" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         </is>
       </c>
       <c r="D332" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         </is>
       </c>
       <c r="D341" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="D350" s="2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         </is>
       </c>
       <c r="D359" s="2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         </is>
       </c>
       <c r="D360" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         </is>
       </c>
       <c r="D377" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         </is>
       </c>
       <c r="D386" s="2" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         </is>
       </c>
       <c r="D395" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         </is>
       </c>
       <c r="D396" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         </is>
       </c>
       <c r="D404" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         </is>
       </c>
       <c r="D413" s="2" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="D423" s="2" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         </is>
       </c>
       <c r="D424" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         </is>
       </c>
       <c r="D433" s="2" t="n">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         </is>
       </c>
       <c r="D443" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         </is>
       </c>
       <c r="D452" s="2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>

--- a/panele-sterowania/Panel-C.xlsx
+++ b/panele-sterowania/Panel-C.xlsx
@@ -524,7 +524,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wygenerowano: 2026-07-19</t>
+          <t>Wygenerowano: 2026-07-21</t>
         </is>
       </c>
     </row>

--- a/panele-sterowania/Panel-C.xlsx
+++ b/panele-sterowania/Panel-C.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stale-walki" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auto-walka" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stale-moc" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oblezenie" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macierz-jednostek" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jednostki-staty" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moc-jednostek" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koszty-jednostek" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Countery" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teren-walka" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stale-walki" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Auto-walka" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stale-moc" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Oblezenie" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Macierz-jednostek" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Jednostki-staty" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Moc-jednostek" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Koszty-jednostek" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Countery" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Teren-walka" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,7 +524,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wygenerowano: 2026-07-21</t>
+          <t>Wygenerowano: 2026-07-24</t>
         </is>
       </c>
     </row>
@@ -51664,7 +51664,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
